--- a/stories/arbres/ATOM-DIF.COR.002-02.xlsx
+++ b/stories/arbres/ATOM-DIF.COR.002-02.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -823,6 +823,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -837,7 +849,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1131,6 +1143,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1155,7 +1172,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Nora est au parc avec maman. Lila arrive. Elles n'ont pas la même taille. Lila est plus petite. Nora est plus grande. Les tailles sont différentes. Les corps ont des formes différentes. Un petit rire commence. Maman parle tout de suite. Maman dit : le corps n'est pas une blague. On joue ensemble. Nora ferme la bouche. Elle tend le ballon. Elles jouent. Le ballon est doux. Plus tard, elles rentrent en classe. Sur la table, il y a de la pâte. Les tabliers tombent différemment. Encore un petit rire. Nora dit : le corps n'est pas une blague. On joue ensemble. Elles font des formes. La pâte est froide. Au parc, puis en classe, c'est pareil. On joue. On ne commente pas le corps pour rabaisser. L'amitié ne dépend pas de la forme.</t>
+          <t>Nora est au parc avec maman. Lila arrive. Elles n'ont pas la même taille. Lila est plus petite. Nora est plus grande. Les tailles sont différentes. Les corps ont des formes différentes. Un petit rire commence. Maman parle tout de suite. Le corps n'est pas une blague. On joue ensemble. Nora ferme la bouche. Elle tend le ballon. Elles jouent. Le ballon est doux. Plus tard, elles rentrent en classe. Sur la table, il y a de la pâte. Les tabliers tombent différemment. Encore un petit rire. Le corps n'est pas une blague. On joue ensemble. Elles font des formes. La pâte est froide. Au parc, puis en classe, c'est pareil. On joue. On ne commente pas le corps pour rabaisser. L'amitié ne dépend pas de la forme.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1293,6 +1310,15 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Nora est au parc avec maman. Lila arrive. Elles n'ont pas la même taille. Lila est plus petite. Nora est plus grande. Les tailles sont différentes. Les corps ont des formes différentes. Un petit rire commence. Maman parle tout de suite.
+maman|Le corps n'est pas une blague. On joue ensemble.
+narrateur|Nora ferme la bouche. Elle tend le ballon. Elles jouent. Le ballon est doux. Plus tard, elles rentrent en classe. Sur la table, il y a de la pâte. Les tabliers tombent différemment. Encore un petit rire.
+enfant-f|Le corps n'est pas une blague. On joue ensemble. Elles font des formes.
+narrateur|La pâte est froide. Au parc, puis en classe, c'est pareil. On joue. On ne commente pas le corps pour rabaisser. L'amitié ne dépend pas de la forme.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1473,6 +1499,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Le corps n'est pas une blague. Que fait-on ?</t>
         </is>
       </c>
     </row>
@@ -1641,6 +1672,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Nora a entendu maman. Le corps n'est pas une blague. Nora et Lila ont joué. Deux fois.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1799,6 +1835,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Nora range un morceau de pâte. Lila range un emporte-pièce. Merci, dit maman.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1961,6 +2002,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1979,7 +2025,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1996,6 +2042,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-DIF.COR.002-02.xlsx
+++ b/stories/arbres/ATOM-DIF.COR.002-02.xlsx
@@ -849,7 +849,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1148,6 +1148,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1319,6 +1324,11 @@
 narrateur|La pâte est froide. Au parc, puis en classe, c'est pareil. On joue. On ne commente pas le corps pour rabaisser. L'amitié ne dépend pas de la forme.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1506,6 +1516,7 @@
           <t>narrateur|Le corps n'est pas une blague. Que fait-on ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1677,6 +1688,7 @@
           <t>narrateur|Nora a entendu maman. Le corps n'est pas une blague. Nora et Lila ont joué. Deux fois.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1840,6 +1852,7 @@
           <t>narrateur|Nora range un morceau de pâte. Lila range un emporte-pièce. Merci, dit maman.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2007,6 +2020,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2025,7 +2039,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2049,6 +2063,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2063,7 +2091,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2250,6 +2278,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-DIF.COR.002-02.xlsx
+++ b/stories/arbres/ATOM-DIF.COR.002-02.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Nora joue, le corps n'est pas une blague</t>
+          <t>La feuille collée à la grille</t>
         </is>
       </c>
     </row>
@@ -835,6 +835,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Une feuille mouillée colle à la grille du parc. Amir et Victorino jouent au ballon, puis à la pâte. Le corps n'est pas une blague. Ils jouent ensemble, deux fois.</t>
         </is>
       </c>
     </row>
@@ -1177,7 +1189,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Nora est au parc avec maman. Lila arrive. Elles n'ont pas la même taille. Lila est plus petite. Nora est plus grande. Les tailles sont différentes. Les corps ont des formes différentes. Un petit rire commence. Maman parle tout de suite. Le corps n'est pas une blague. On joue ensemble. Nora ferme la bouche. Elle tend le ballon. Elles jouent. Le ballon est doux. Plus tard, elles rentrent en classe. Sur la table, il y a de la pâte. Les tabliers tombent différemment. Encore un petit rire. Le corps n'est pas une blague. On joue ensemble. Elles font des formes. La pâte est froide. Au parc, puis en classe, c'est pareil. On joue. On ne commente pas le corps pour rabaisser. L'amitié ne dépend pas de la forme.</t>
+          <t>Une feuille mouillée colle à la grille du parc. Elle est verte, avec une nervure brillante. Le gravier croque sous les chaussures. Un ballon rouge dort sous un buisson. Le banc a encore une trace de pluie. Le sac de maman pose contre le pied du banc. En ce moment, Amir tire la feuille. Elle est collée, hein, Amir ? Oui. Elle est froide. La feuille se décolle avec un petit bruit. Amir la pose sur le banc. Victorino arrive. Ils n'ont pas la même taille. Victorino est plus petit. Amir est plus grand. Les tailles sont différentes. Les corps ont des formes différentes. Un petit rire commence. Le corps n'est pas une blague. On joue ensemble. Amir ferme la bouche. Il tend le ballon rouge. On joue ? Oui. Le ballon est doux. Il sent un peu le caoutchouc. Ils se le passent sur le gravier. Bravo. Vous jouez. C'est ça. Plus tard, ils rentrent en classe. Sur la table, il y a de la pâte. La pâte est froide et un peu grise. Les tabliers tombent différemment. Encore un petit rire. Le corps n'est pas une blague. On joue ensemble. Oui, Amir. Tu t'en souviens. Ils font des formes. Amir presse un rond. Victorino presse une étoile. La pâte colle un peu aux ongles. Au parc, puis en classe, c'est pareil. On joue. L'amitié ne dépend pas de la forme. Amir pose le rond à côté de l'étoile. Ils sont amis. Oui. Comme vous. La pâte est froide, hein ? Oui. Et douce.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1317,11 +1329,53 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Nora est au parc avec maman. Lila arrive. Elles n'ont pas la même taille. Lila est plus petite. Nora est plus grande. Les tailles sont différentes. Les corps ont des formes différentes. Un petit rire commence. Maman parle tout de suite.
-maman|Le corps n'est pas une blague. On joue ensemble.
-narrateur|Nora ferme la bouche. Elle tend le ballon. Elles jouent. Le ballon est doux. Plus tard, elles rentrent en classe. Sur la table, il y a de la pâte. Les tabliers tombent différemment. Encore un petit rire.
-enfant-f|Le corps n'est pas une blague. On joue ensemble. Elles font des formes.
-narrateur|La pâte est froide. Au parc, puis en classe, c'est pareil. On joue. On ne commente pas le corps pour rabaisser. L'amitié ne dépend pas de la forme.</t>
+          <t>narrateur|Une feuille mouillée colle à la grille du parc.
+narrateur|Elle est verte, avec une nervure brillante.
+narrateur|Le gravier croque sous les chaussures.
+narrateur|Un ballon rouge dort sous un buisson.
+narrateur|Le banc a encore une trace de pluie.
+narrateur|Le sac de maman pose contre le pied du banc.
+narrateur|En ce moment, Amir tire la feuille.
+maman|Elle est collée, hein, Amir ?
+enfant-m|Oui. Elle est froide.
+narrateur|La feuille se décolle avec un petit bruit.
+narrateur|Amir la pose sur le banc.
+narrateur|Victorino arrive.
+narrateur|Ils n'ont pas la même taille.
+narrateur|Victorino est plus petit.
+narrateur|Amir est plus grand.
+narrateur|Les tailles sont différentes.
+narrateur|Les corps ont des formes différentes.
+narrateur|Un petit rire commence.
+maman|Le corps n'est pas une blague.
+maman|On joue ensemble.
+narrateur|Amir ferme la bouche.
+narrateur|Il tend le ballon rouge.
+enfant-m|On joue ?
+copain|Oui.
+narrateur|Le ballon est doux.
+narrateur|Il sent un peu le caoutchouc.
+narrateur|Ils se le passent sur le gravier.
+maman|Bravo. Vous jouez. C'est ça.
+narrateur|Plus tard, ils rentrent en classe.
+narrateur|Sur la table, il y a de la pâte.
+narrateur|La pâte est froide et un peu grise.
+narrateur|Les tabliers tombent différemment.
+narrateur|Encore un petit rire.
+enfant-m|Le corps n'est pas une blague.
+enfant-m|On joue ensemble.
+maman|Oui, Amir. Tu t'en souviens.
+narrateur|Ils font des formes.
+narrateur|Amir presse un rond.
+narrateur|Victorino presse une étoile.
+narrateur|La pâte colle un peu aux ongles.
+maman|Au parc, puis en classe, c'est pareil.
+maman|On joue. L'amitié ne dépend pas de la forme.
+narrateur|Amir pose le rond à côté de l'étoile.
+copain|Ils sont amis.
+maman|Oui. Comme vous.
+maman|La pâte est froide, hein ?
+enfant-m|Oui. Et douce.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1513,7 +1567,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Le corps n'est pas une blague. Que fait-on ?</t>
+          <t>narrateur|Le corps n'est pas une blague.
+narrateur|Que fait-on ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1541,7 +1596,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Nora a entendu maman. Le corps n'est pas une blague. Nora et Lila ont joué. Deux fois.</t>
+          <t>Amir a entendu maman. Le corps n'est pas une blague. Amir et Victorino ont joué. Deux fois. Au parc, puis en classe. Bravo, Amir. Tu as fait du bon travail. Tu as tendu le ballon. Tu as pressé la pâte. Le rond et l'étoile restent sur la table. On les garde ? On les laisse sécher un peu. Moi je garde l'étoile. Moi le rond.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1685,7 +1740,17 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Nora a entendu maman. Le corps n'est pas une blague. Nora et Lila ont joué. Deux fois.</t>
+          <t>narrateur|Amir a entendu maman.
+narrateur|Le corps n'est pas une blague.
+narrateur|Amir et Victorino ont joué.
+narrateur|Deux fois. Au parc, puis en classe.
+maman|Bravo, Amir. Tu as fait du bon travail.
+maman|Tu as tendu le ballon. Tu as pressé la pâte.
+narrateur|Le rond et l'étoile restent sur la table.
+enfant-m|On les garde ?
+maman|On les laisse sécher un peu.
+copain|Moi je garde l'étoile.
+enfant-m|Moi le rond.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1713,7 +1778,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Nora range un morceau de pâte. Lila range un emporte-pièce. Merci, dit maman.</t>
+          <t>Amir range un morceau de pâte. Victorino range un emporte-pièce. Tu as fini de ranger la pâte ? Oui, maman. Merci. Bravo. Dans la poche d'Amir, la feuille a séché. Elle est plus légère. La feuille du parc. On la posera sur le rebord, à la maison. La classe sent encore la pâte froide.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1849,7 +1914,16 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Nora range un morceau de pâte. Lila range un emporte-pièce. Merci, dit maman.</t>
+          <t>narrateur|Amir range un morceau de pâte.
+narrateur|Victorino range un emporte-pièce.
+maman|Tu as fini de ranger la pâte ?
+enfant-m|Oui, maman.
+maman|Merci. Bravo.
+narrateur|Dans la poche d'Amir, la feuille a séché.
+narrateur|Elle est plus légère.
+enfant-m|La feuille du parc.
+maman|On la posera sur le rebord, à la maison.
+narrateur|La classe sent encore la pâte froide.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1877,7 +1951,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a joué deux fois. Le corps n'est pas une blague. On joue. Bravo. C'était du bon travail. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2017,7 +2091,10 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|On a joué deux fois.
+maman|Le corps n'est pas une blague. On joue.
+maman|Bravo. C'était du bon travail.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2039,7 +2116,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2077,6 +2154,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-DIF.COR.002-02.xlsx
+++ b/stories/arbres/ATOM-DIF.COR.002-02.xlsx
@@ -1189,7 +1189,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Une feuille mouillée colle à la grille du parc. Elle est verte, avec une nervure brillante. Le gravier croque sous les chaussures. Un ballon rouge dort sous un buisson. Le banc a encore une trace de pluie. Le sac de maman pose contre le pied du banc. En ce moment, Amir tire la feuille. Elle est collée, hein, Amir ? Oui. Elle est froide. La feuille se décolle avec un petit bruit. Amir la pose sur le banc. Victorino arrive. Ils n'ont pas la même taille. Victorino est plus petit. Amir est plus grand. Les tailles sont différentes. Les corps ont des formes différentes. Un petit rire commence. Le corps n'est pas une blague. On joue ensemble. Amir ferme la bouche. Il tend le ballon rouge. On joue ? Oui. Le ballon est doux. Il sent un peu le caoutchouc. Ils se le passent sur le gravier. Bravo. Vous jouez. C'est ça. Plus tard, ils rentrent en classe. Sur la table, il y a de la pâte. La pâte est froide et un peu grise. Les tabliers tombent différemment. Encore un petit rire. Le corps n'est pas une blague. On joue ensemble. Oui, Amir. Tu t'en souviens. Ils font des formes. Amir presse un rond. Victorino presse une étoile. La pâte colle un peu aux ongles. Au parc, puis en classe, c'est pareil. On joue. L'amitié ne dépend pas de la forme. Amir pose le rond à côté de l'étoile. Ils sont amis. Oui. Comme vous. La pâte est froide, hein ? Oui. Et douce.</t>
+          <t>Une feuille mouillée colle à la grille du parc. Elle est verte, avec une nervure brillante. Le gravier croque sous les chaussures. Un ballon rouge dort sous un buisson. Le banc a encore une trace de pluie. Le sac de maman pose contre le pied du banc. En ce moment, Amir tire la feuille. Elle est collée, hein, Amir ? Oui. Elle est froide. La feuille se décolle avec un petit bruit. Amir la pose sur le banc. Victorino arrive. Ils n'ont pas la même taille. Victorino est plus petit. Amir est plus grand. Les tailles sont différentes. Les corps ont des formes différentes. Un petit rire commence. Le corps n'est pas une blague. On joue ensemble. Amir ferme la bouche. Il tend le ballon rouge. On joue ? Oui. Le ballon est doux. Il sent un peu le caoutchouc. Ils se le passent sur le gravier. Bravo. Vous jouez. C'est ça. Plus tard, ils rentrent en classe. Sur la table, il y a de la pâte. La pâte est froide et un peu grise. Les tabliers tombent différemment. Encore un petit rire. Le corps n'est pas une blague. On joue ensemble. Oui, Amir. Tu t'en souviens. Ils font des formes. Amir presse un rond. Victorino presse une étoile. La pâte colle un peu aux ongles. Au parc, puis en classe, c'est pareil. On joue. L'amitié ne dépend pas de la forme. Amir pose le rond à côté de l'étoile. Ils sont amis. Oui. Comme vous. La pâte est froide, hein ? Oui. Et douce. Un rayon entre par la fenêtre de la classe. Il touche l'étoile de pâte. L'étoile brille un peu. La mienne brille. La mienne aussi. Vous jouez. C'est ça. Amir lisse le bord du rond. Victorino lisse une branche de l'étoile. La pâte fait un petit bruit de tapis mou.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1337,7 +1337,8 @@
 narrateur|Le sac de maman pose contre le pied du banc.
 narrateur|En ce moment, Amir tire la feuille.
 maman|Elle est collée, hein, Amir ?
-enfant-m|Oui. Elle est froide.
+enfant-m|Oui.
+enfant-m|Elle est froide.
 narrateur|La feuille se décolle avec un petit bruit.
 narrateur|Amir la pose sur le banc.
 narrateur|Victorino arrive.
@@ -1356,7 +1357,9 @@
 narrateur|Le ballon est doux.
 narrateur|Il sent un peu le caoutchouc.
 narrateur|Ils se le passent sur le gravier.
-maman|Bravo. Vous jouez. C'est ça.
+maman|Bravo.
+maman|Vous jouez.
+maman|C'est ça.
 narrateur|Plus tard, ils rentrent en classe.
 narrateur|Sur la table, il y a de la pâte.
 narrateur|La pâte est froide et un peu grise.
@@ -1364,18 +1367,32 @@
 narrateur|Encore un petit rire.
 enfant-m|Le corps n'est pas une blague.
 enfant-m|On joue ensemble.
-maman|Oui, Amir. Tu t'en souviens.
+maman|Oui, Amir.
+maman|Tu t'en souviens.
 narrateur|Ils font des formes.
 narrateur|Amir presse un rond.
 narrateur|Victorino presse une étoile.
 narrateur|La pâte colle un peu aux ongles.
 maman|Au parc, puis en classe, c'est pareil.
-maman|On joue. L'amitié ne dépend pas de la forme.
+maman|On joue.
+maman|L'amitié ne dépend pas de la forme.
 narrateur|Amir pose le rond à côté de l'étoile.
 copain|Ils sont amis.
-maman|Oui. Comme vous.
+maman|Oui.
+maman|Comme vous.
 maman|La pâte est froide, hein ?
-enfant-m|Oui. Et douce.</t>
+enfant-m|Oui.
+enfant-m|Et douce.
+narrateur|Un rayon entre par la fenêtre de la classe.
+narrateur|Il touche l'étoile de pâte.
+narrateur|L'étoile brille un peu.
+copain|La mienne brille.
+enfant-m|La mienne aussi.
+maman|Vous jouez.
+maman|C'est ça.
+narrateur|Amir lisse le bord du rond.
+narrateur|Victorino lisse une branche de l'étoile.
+narrateur|La pâte fait un petit bruit de tapis mou.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1743,9 +1760,12 @@
           <t>narrateur|Amir a entendu maman.
 narrateur|Le corps n'est pas une blague.
 narrateur|Amir et Victorino ont joué.
-narrateur|Deux fois. Au parc, puis en classe.
-maman|Bravo, Amir. Tu as fait du bon travail.
-maman|Tu as tendu le ballon. Tu as pressé la pâte.
+narrateur|Deux fois.
+narrateur|Au parc, puis en classe.
+maman|Bravo, Amir.
+maman|Tu as fait du bon travail.
+maman|Tu as tendu le ballon.
+maman|Tu as pressé la pâte.
 narrateur|Le rond et l'étoile restent sur la table.
 enfant-m|On les garde ?
 maman|On les laisse sécher un peu.
@@ -1918,7 +1938,8 @@
 narrateur|Victorino range un emporte-pièce.
 maman|Tu as fini de ranger la pâte ?
 enfant-m|Oui, maman.
-maman|Merci. Bravo.
+maman|Merci.
+maman|Bravo.
 narrateur|Dans la poche d'Amir, la feuille a séché.
 narrateur|Elle est plus légère.
 enfant-m|La feuille du parc.
@@ -2092,8 +2113,10 @@
       <c r="AW6" t="inlineStr">
         <is>
           <t>enfant-m|On a joué deux fois.
-maman|Le corps n'est pas une blague. On joue.
-maman|Bravo. C'était du bon travail.
+maman|Le corps n'est pas une blague.
+maman|On joue.
+maman|Bravo.
+maman|C'était du bon travail.
 narrateur|L'histoire est finie.</t>
         </is>
       </c>
@@ -2116,7 +2139,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2159,6 +2182,34 @@
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>

--- a/stories/arbres/ATOM-DIF.COR.002-02.xlsx
+++ b/stories/arbres/ATOM-DIF.COR.002-02.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>La feuille collée à la grille</t>
+          <t>Le cheval de bois sous la haie</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Une feuille mouillée colle à la grille du parc. Amir et Victorino jouent au ballon, puis à la pâte. Le corps n'est pas une blague. Ils jouent ensemble, deux fois.</t>
+          <t>Amir cherche son cheval de bois sous la haie. Victorino l'aide. Un rire commence. Maman dit : le corps n'est pas une blague. Sur la véranda, ils font une écurie d'argile.</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Une feuille mouillée colle à la grille du parc. Elle est verte, avec une nervure brillante. Le gravier croque sous les chaussures. Un ballon rouge dort sous un buisson. Le banc a encore une trace de pluie. Le sac de maman pose contre le pied du banc. En ce moment, Amir tire la feuille. Elle est collée, hein, Amir ? Oui. Elle est froide. La feuille se décolle avec un petit bruit. Amir la pose sur le banc. Victorino arrive. Ils n'ont pas la même taille. Victorino est plus petit. Amir est plus grand. Les tailles sont différentes. Les corps ont des formes différentes. Un petit rire commence. Le corps n'est pas une blague. On joue ensemble. Amir ferme la bouche. Il tend le ballon rouge. On joue ? Oui. Le ballon est doux. Il sent un peu le caoutchouc. Ils se le passent sur le gravier. Bravo. Vous jouez. C'est ça. Plus tard, ils rentrent en classe. Sur la table, il y a de la pâte. La pâte est froide et un peu grise. Les tabliers tombent différemment. Encore un petit rire. Le corps n'est pas une blague. On joue ensemble. Oui, Amir. Tu t'en souviens. Ils font des formes. Amir presse un rond. Victorino presse une étoile. La pâte colle un peu aux ongles. Au parc, puis en classe, c'est pareil. On joue. L'amitié ne dépend pas de la forme. Amir pose le rond à côté de l'étoile. Ils sont amis. Oui. Comme vous. La pâte est froide, hein ? Oui. Et douce. Un rayon entre par la fenêtre de la classe. Il touche l'étoile de pâte. L'étoile brille un peu. La mienne brille. La mienne aussi. Vous jouez. C'est ça. Amir lisse le bord du rond. Victorino lisse une branche de l'étoile. La pâte fait un petit bruit de tapis mou.</t>
+          <t>La poussière du chemin sent encore le soleil. La haie de buis est chaude et serrée. Une abeille va d'une fleur à l'autre. Le portail de fer est tiède. Un caillou blanc brille dans l'ornière. Tu as vu le portail, Amir ? Il est chaud. Oui. Le soleil l'a touché. En ce moment, Amir cherche dans l'herbe. L'herbe est sèche et un peu piquante. Mon cheval de bois. Il a roulé. Regarde sous la haie. Victorino arrive près du portail. Ses genoux ont déjà de la poussière. Victorino a un corps plus rond. Amir a un corps plus mince. Les corps ont des formes différentes. Un petit rire commence. Le corps n'est pas une blague. On joue. Amir ferme la bouche. On cherche le cheval ? On cherche. Ils écartent une branche. Les feuilles sentent le vert. Un caillou roule. Pas lui. Le bois du cheval apparaît. Te voilà. Il a de la terre au nez. On va le laver à la maison.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Nora est au parc avec maman. Lila arrive. Elles n'ont pas la même taille. Lila est plus petite. Nora est plus grande. Les tailles sont différentes. Les &lt;emphasis level="moderate"&gt;corps&lt;/emphasis&gt; ont des formes différentes. Un petit rire commence. Maman parle tout de suite. Maman dit : le corps n'est pas une blague. On joue ensemble. Nora ferme la bouche. Elle tend le ballon. Elles jouent. Le ballon est doux. Plus tard, elles rentrent en classe. Sur la table, il y a de la pâte. Les tabliers tombent différemment. Encore un petit rire. Nora dit : le corps n'est pas une blague. On joue ensemble. Elles font des formes. La pâte est froide. Au parc, puis en classe, c'est pareil. On joue. On ne commente pas le corps pour rabaisser. L'amitié ne dépend pas de la forme.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>La poussière du chemin sent encore le soleil. La haie de buis est chaude et serrée. Une abeille va d'une fleur à l'autre. Le portail de fer est tiède. Un caillou blanc brille dans l'ornière. Tu as vu le portail, Amir ? Il est chaud. Oui. Le soleil l'a touché. En ce moment, Amir cherche dans l'herbe. L'herbe est sèche et un peu piquante. Mon cheval de bois. Il a roulé. Regarde sous la haie. Victorino arrive près du portail. Ses genoux ont déjà de la poussière. Victorino a un corps plus rond. Amir a un corps plus mince. Les corps ont des formes différentes. Un petit rire commence. Le corps n'est pas une blague. On joue. Amir ferme la bouche. On cherche le cheval ? On cherche. Ils écartent une branche. Les feuilles sentent le vert. Un caillou roule. Pas lui. Le bois du cheval apparaît. Te voilà. Il a de la terre au nez. On va le laver à la maison.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1329,70 +1329,39 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Une feuille mouillée colle à la grille du parc.
-narrateur|Elle est verte, avec une nervure brillante.
-narrateur|Le gravier croque sous les chaussures.
-narrateur|Un ballon rouge dort sous un buisson.
-narrateur|Le banc a encore une trace de pluie.
-narrateur|Le sac de maman pose contre le pied du banc.
-narrateur|En ce moment, Amir tire la feuille.
-maman|Elle est collée, hein, Amir ?
-enfant-m|Oui.
-enfant-m|Elle est froide.
-narrateur|La feuille se décolle avec un petit bruit.
-narrateur|Amir la pose sur le banc.
-narrateur|Victorino arrive.
-narrateur|Ils n'ont pas la même taille.
-narrateur|Victorino est plus petit.
-narrateur|Amir est plus grand.
-narrateur|Les tailles sont différentes.
+          <t>narrateur|La poussière du chemin sent encore le soleil.
+narrateur|La haie de buis est chaude et serrée.
+narrateur|Une abeille va d'une fleur à l'autre.
+narrateur|Le portail de fer est tiède.
+narrateur|Un caillou blanc brille dans l'ornière.
+maman|Tu as vu le portail, Amir ?
+enfant-m|Il est chaud.
+maman|Oui.
+maman|Le soleil l'a touché.
+narrateur|En ce moment, Amir cherche dans l'herbe.
+narrateur|L'herbe est sèche et un peu piquante.
+enfant-m|Mon cheval de bois.
+enfant-m|Il a roulé.
+maman|Regarde sous la haie.
+narrateur|Victorino arrive près du portail.
+narrateur|Ses genoux ont déjà de la poussière.
+narrateur|Victorino a un corps plus rond.
+narrateur|Amir a un corps plus mince.
 narrateur|Les corps ont des formes différentes.
 narrateur|Un petit rire commence.
 maman|Le corps n'est pas une blague.
-maman|On joue ensemble.
+maman|On joue.
 narrateur|Amir ferme la bouche.
-narrateur|Il tend le ballon rouge.
-enfant-m|On joue ?
-copain|Oui.
-narrateur|Le ballon est doux.
-narrateur|Il sent un peu le caoutchouc.
-narrateur|Ils se le passent sur le gravier.
-maman|Bravo.
-maman|Vous jouez.
-maman|C'est ça.
-narrateur|Plus tard, ils rentrent en classe.
-narrateur|Sur la table, il y a de la pâte.
-narrateur|La pâte est froide et un peu grise.
-narrateur|Les tabliers tombent différemment.
-narrateur|Encore un petit rire.
-enfant-m|Le corps n'est pas une blague.
-enfant-m|On joue ensemble.
-maman|Oui, Amir.
-maman|Tu t'en souviens.
-narrateur|Ils font des formes.
-narrateur|Amir presse un rond.
-narrateur|Victorino presse une étoile.
-narrateur|La pâte colle un peu aux ongles.
-maman|Au parc, puis en classe, c'est pareil.
-maman|On joue.
-maman|L'amitié ne dépend pas de la forme.
-narrateur|Amir pose le rond à côté de l'étoile.
-copain|Ils sont amis.
-maman|Oui.
-maman|Comme vous.
-maman|La pâte est froide, hein ?
-enfant-m|Oui.
-enfant-m|Et douce.
-narrateur|Un rayon entre par la fenêtre de la classe.
-narrateur|Il touche l'étoile de pâte.
-narrateur|L'étoile brille un peu.
-copain|La mienne brille.
-enfant-m|La mienne aussi.
-maman|Vous jouez.
-maman|C'est ça.
-narrateur|Amir lisse le bord du rond.
-narrateur|Victorino lisse une branche de l'étoile.
-narrateur|La pâte fait un petit bruit de tapis mou.</t>
+enfant-m|On cherche le cheval ?
+copain|On cherche.
+narrateur|Ils écartent une branche.
+narrateur|Les feuilles sentent le vert.
+narrateur|Un caillou roule.
+enfant-m|Pas lui.
+narrateur|Le bois du cheval apparaît.
+enfant-m|Te voilà.
+copain|Il a de la terre au nez.
+maman|On va le laver à la maison.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1429,7 +1398,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le &lt;emphasis level="moderate"&gt;corps&lt;/emphasis&gt; n'est pas une blague. Que fait-on ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le corps n'est pas une blague. Que fait-on ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1444,7 +1413,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>jouer | on joue | pas une blague | pas blague</t>
+          <t>jouer | on joue | pas une blague | pas blague | le cheval | l'écurie</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1588,7 +1557,6 @@
 narrateur|Que fait-on ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1613,12 +1581,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Amir a entendu maman. Le corps n'est pas une blague. Amir et Victorino ont joué. Deux fois. Au parc, puis en classe. Bravo, Amir. Tu as fait du bon travail. Tu as tendu le ballon. Tu as pressé la pâte. Le rond et l'étoile restent sur la table. On les garde ? On les laisse sécher un peu. Moi je garde l'étoile. Moi le rond.</t>
+          <t>Sur la véranda, l'argile attend. Elle est froide et un peu grise. Amir lave le cheval. L'eau fait un filet brun. Le bois redevient lisse. Il est propre. Il a besoin d'une écurie. On la fait. Ils pressent l'argile. Ça fait un bruit mou. Amir dresse un mur. Victorino dresse l'autre mur. Un mur s'affaisse. Il est fatigué. On le tient ensemble. Victorino appuie tout doux. Amir pose un toit plat. Le cheval entre dans l'écurie. Sa jambe de bois touche l'argile. Il est à la maison. Bravo, Amir. Tu as trouvé le cheval. Vous jouez. L'amitié ne dépend pas de la forme.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Nora a entendu maman. Le &lt;emphasis level="moderate"&gt;corps&lt;/emphasis&gt; n'est pas une blague. Nora et Lila ont joué. Deux fois.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Sur la véranda, l'argile attend. Elle est froide et un peu grise. Amir lave le cheval. L'eau fait un filet brun. Le bois redevient lisse. Il est propre. Il a besoin d'une écurie. On la fait. Ils pressent l'argile. Ça fait un bruit mou. Amir dresse un mur. Victorino dresse l'autre mur. Un mur s'affaisse. Il est fatigué. On le tient ensemble. Victorino appuie tout doux. Amir pose un toit plat. Le cheval entre dans l'écurie. Sa jambe de bois touche l'argile. Il est à la maison. Bravo, Amir. Tu as trouvé le cheval. Vous jouez. L'amitié ne dépend pas de la forme.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1757,23 +1725,32 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Amir a entendu maman.
-narrateur|Le corps n'est pas une blague.
-narrateur|Amir et Victorino ont joué.
-narrateur|Deux fois.
-narrateur|Au parc, puis en classe.
+          <t>narrateur|Sur la véranda, l'argile attend.
+narrateur|Elle est froide et un peu grise.
+narrateur|Amir lave le cheval.
+narrateur|L'eau fait un filet brun.
+narrateur|Le bois redevient lisse.
+enfant-m|Il est propre.
+maman|Il a besoin d'une écurie.
+copain|On la fait.
+narrateur|Ils pressent l'argile.
+narrateur|Ça fait un bruit mou.
+narrateur|Amir dresse un mur.
+narrateur|Victorino dresse l'autre mur.
+narrateur|Un mur s'affaisse.
+enfant-m|Il est fatigué.
+maman|On le tient ensemble.
+narrateur|Victorino appuie tout doux.
+narrateur|Amir pose un toit plat.
+narrateur|Le cheval entre dans l'écurie.
+narrateur|Sa jambe de bois touche l'argile.
+copain|Il est à la maison.
 maman|Bravo, Amir.
-maman|Tu as fait du bon travail.
-maman|Tu as tendu le ballon.
-maman|Tu as pressé la pâte.
-narrateur|Le rond et l'étoile restent sur la table.
-enfant-m|On les garde ?
-maman|On les laisse sécher un peu.
-copain|Moi je garde l'étoile.
-enfant-m|Moi le rond.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+maman|Tu as trouvé le cheval.
+maman|Vous jouez.
+maman|L'amitié ne dépend pas de la forme.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1798,12 +1775,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Amir range un morceau de pâte. Victorino range un emporte-pièce. Tu as fini de ranger la pâte ? Oui, maman. Merci. Bravo. Dans la poche d'Amir, la feuille a séché. Elle est plus légère. La feuille du parc. On la posera sur le rebord, à la maison. La classe sent encore la pâte froide.</t>
+          <t>On laisse sécher ? Oui. L'argile devient un peu plus claire. Le cheval de bois attend dessous. Il dort. Tout petit. Tu as fini de presser l'argile ? Oui, maman. Ils se lavent les mains. L'eau est tiède. Dehors, le portail est encore chaud. Une abeille passe encore près de la haie. On le touchera demain. Merci, Victorino. Merci, Amir.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Nora range un morceau de pâte. Lila range un emporte-pièce. Merci, dit maman.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>On laisse sécher ? Oui. L'argile devient un peu plus claire. Le cheval de bois attend dessous. Il dort. Tout petit. Tu as fini de presser l'argile ? Oui, maman. Ils se lavent les mains. L'eau est tiède. Dehors, le portail est encore chaud. Une abeille passe encore près de la haie. On le touchera demain. Merci, Victorino. Merci, Amir.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1934,20 +1911,23 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Amir range un morceau de pâte.
-narrateur|Victorino range un emporte-pièce.
-maman|Tu as fini de ranger la pâte ?
+          <t>maman|On laisse sécher ?
+enfant-m|Oui.
+narrateur|L'argile devient un peu plus claire.
+narrateur|Le cheval de bois attend dessous.
+copain|Il dort.
+enfant-m|Tout petit.
+maman|Tu as fini de presser l'argile ?
 enfant-m|Oui, maman.
-maman|Merci.
-maman|Bravo.
-narrateur|Dans la poche d'Amir, la feuille a séché.
-narrateur|Elle est plus légère.
-enfant-m|La feuille du parc.
-maman|On la posera sur le rebord, à la maison.
-narrateur|La classe sent encore la pâte froide.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+narrateur|Ils se lavent les mains.
+narrateur|L'eau est tiède.
+narrateur|Dehors, le portail est encore chaud.
+narrateur|Une abeille passe encore près de la haie.
+maman|On le touchera demain.
+enfant-m|Merci, Victorino.
+copain|Merci, Amir.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1972,12 +1952,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>On a joué deux fois. Le corps n'est pas une blague. On joue. Bravo. C'était du bon travail. L'histoire est finie.</t>
+          <t>On a trouvé le cheval. On a fait l'écurie. Vous avez joué. La haie garde un peu de poussière. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>On a trouvé le cheval. On a fait l'écurie. Vous avez joué. La haie garde un peu de poussière. L'histoire est finie.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2033,14 +2013,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>slow</t>
         </is>
       </c>
       <c r="AA6" s="2" t="n">
         <v>0.92</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2112,15 +2092,13 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>enfant-m|On a joué deux fois.
-maman|Le corps n'est pas une blague.
-maman|On joue.
-maman|Bravo.
-maman|C'était du bon travail.
+          <t>enfant-m|On a trouvé le cheval.
+copain|On a fait l'écurie.
+maman|Vous avez joué.
+narrateur|La haie garde un peu de poussière.
 narrateur|L'histoire est finie.</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2139,7 +2117,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2212,6 +2190,13 @@
       <c r="A10" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-DIF.COR.002-02.xlsx
+++ b/stories/arbres/ATOM-DIF.COR.002-02.xlsx
@@ -1952,12 +1952,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>On a trouvé le cheval. On a fait l'écurie. Vous avez joué. La haie garde un peu de poussière. L'histoire est finie.</t>
+          <t>On a trouvé le cheval. On a fait l'écurie. Vous avez joué. La haie garde un peu de poussière.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>On a trouvé le cheval. On a fait l'écurie. Vous avez joué. La haie garde un peu de poussière. L'histoire est finie.</t>
+          <t>On a trouvé le cheval. On a fait l'écurie. Vous avez joué. La haie garde un peu de poussière.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2095,8 +2095,7 @@
           <t>enfant-m|On a trouvé le cheval.
 copain|On a fait l'écurie.
 maman|Vous avez joué.
-narrateur|La haie garde un peu de poussière.
-narrateur|L'histoire est finie.</t>
+narrateur|La haie garde un peu de poussière.</t>
         </is>
       </c>
     </row>
@@ -2117,7 +2116,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2195,6 +2194,13 @@
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>

--- a/stories/arbres/ATOM-DIF.COR.002-02.xlsx
+++ b/stories/arbres/ATOM-DIF.COR.002-02.xlsx
@@ -676,7 +676,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>parc puis classe</t>
+          <t>chemin du village puis véranda</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Nora, Lila, maman</t>
+          <t>Amir, Victorino, maman</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-DIF.COR.002-02.xlsx
+++ b/stories/arbres/ATOM-DIF.COR.002-02.xlsx
@@ -676,7 +676,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>chemin du village puis véranda</t>
+          <t>chemin du village puis véranda, haie de buis, poussière, abeille</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Amir, Victorino, maman</t>
+          <t>Amir, Victorino, papa, maman</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Amir cherche son cheval de bois sous la haie. Victorino l'aide. Un rire commence. Maman dit : le corps n'est pas une blague. Sur la véranda, ils font une écurie d'argile.</t>
+          <t>Le chemin du village sent la poussière chaude. La haie de buis pique. Une abeille va d'une fleur à l'autre. Sur une feuille, un éclat de buis brille. Amir veut son cheval de bois, maintenant, sous la haie. Il écarte trop vite : le bois glisse, l'éclat saute. Victorino s'agenouille lentement. Un petit rire commence, puis s'arrête. Ils cherchent ensemble. Merci vécu. Sur la véranda, l'écurie d'argile s'affaisse. Amir refuse de foncer. L'éclat de buis tient.</t>
         </is>
       </c>
     </row>
@@ -1189,17 +1189,17 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>La poussière du chemin sent encore le soleil. La haie de buis est chaude et serrée. Une abeille va d'une fleur à l'autre. Le portail de fer est tiède. Un caillou blanc brille dans l'ornière. Tu as vu le portail, Amir ? Il est chaud. Oui. Le soleil l'a touché. En ce moment, Amir cherche dans l'herbe. L'herbe est sèche et un peu piquante. Mon cheval de bois. Il a roulé. Regarde sous la haie. Victorino arrive près du portail. Ses genoux ont déjà de la poussière. Victorino a un corps plus rond. Amir a un corps plus mince. Les corps ont des formes différentes. Un petit rire commence. Le corps n'est pas une blague. On joue. Amir ferme la bouche. On cherche le cheval ? On cherche. Ils écartent une branche. Les feuilles sentent le vert. Un caillou roule. Pas lui. Le bois du cheval apparaît. Te voilà. Il a de la terre au nez. On va le laver à la maison.</t>
+          <t>Le chemin du village sent la poussière chaude. La haie de buis est serrée, un peu piquante. Une abeille va d'une fleur à l'autre. Le portail de fer est tiède sous la main. Tu as vu le portail, Amir ? Il est chaud. Le soleil l'a touché. La haie aussi. Elle pique un peu. La poussière colle aux orteils. Le buis sent le vert chaud. Une feuille tremble au bord de la haie. Sur la feuille, un éclat de buis brille. Il brille, papa. Tu le vois, sur la feuille ? Oui, il brille. C'est petit, cet éclat. L'herbe est sèche, un peu dure. Mon cheval de bois. Il a roulé. Sous la haie ? Oui, maman. Je le veux, maintenant ! On le cherche ? Oui, papa. En ce moment, Amir cherche dans l'herbe. Les tiges piquent ses paumes. Il écarte une branche trop vite. Le bois glisse plus loin, sous les feuilles. Il est parti ! L'éclat de buis saute près du portail. Le sourire d'Amir disparaît. Dans sa poitrine, l'envie et l'inquiétude se bousculent. Ses épaules tombent un peu. Papa s'accroupit à la même hauteur. Tu veux le cheval ? Oui, papa. Tes genoux sont dans l'herbe ? Oui, maman. Victorino arrive près du portail. Il prend son temps, les pieds dans la poussière. J'aide. Vite ! Victorino s'agenouille plus lentement. Un petit rire commence, chez Amir. Victorino baisse les yeux. Ses épaules se serrent un peu. Le rire s'arrête net. Amir ferme la bouche. Ses joues sont chaudes, un peu. On cherche le cheval ? Victorino ne répond pas tout de suite. On cherche. Tu tiens la branche, Amir ? Oui.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>La poussière du chemin sent encore le soleil. La haie de buis est chaude et serrée. Une abeille va d'une fleur à l'autre. Le portail de fer est tiède. Un caillou blanc brille dans l'ornière. Tu as vu le portail, Amir ? Il est chaud. Oui. Le soleil l'a touché. En ce moment, Amir cherche dans l'herbe. L'herbe est sèche et un peu piquante. Mon cheval de bois. Il a roulé. Regarde sous la haie. Victorino arrive près du portail. Ses genoux ont déjà de la poussière. Victorino a un corps plus rond. Amir a un corps plus mince. Les corps ont des formes différentes. Un petit rire commence. Le corps n'est pas une blague. On joue. Amir ferme la bouche. On cherche le cheval ? On cherche. Ils écartent une branche. Les feuilles sentent le vert. Un caillou roule. Pas lui. Le bois du cheval apparaît. Te voilà. Il a de la terre au nez. On va le laver à la maison.</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le chemin du village sent la poussière chaude. La haie de buis est serrée, un peu piquante. Une abeille va d'une fleur à l'autre. Le portail de fer est tiède sous la main. Tu as vu le portail, Amir ? Il est chaud. Le soleil l'a touché. La haie aussi. Elle pique un peu. La poussière colle aux orteils. Le buis sent le vert chaud. Une feuille tremble au bord de la haie. Sur la feuille, un &lt;emphasis level="moderate"&gt;éclat de buis&lt;/emphasis&gt; brille. Il brille, papa. Tu le vois, sur la feuille ? Oui, il brille. C'est petit, cet éclat. L'herbe est sèche, un peu dure. Mon cheval de bois. Il a roulé. Sous la haie ? Oui, maman. Je le veux, maintenant ! On le cherche ? Oui, papa. En ce moment, Amir cherche dans l'herbe. Les tiges piquent ses paumes. Il écarte une branche trop vite. Le bois glisse plus loin, sous les feuilles. Il est parti ! L'éclat de buis saute près du portail. Le sourire d'Amir disparaît. Dans sa poitrine, l'envie et l'inquiétude se bousculent. Ses épaules tombent un peu. Papa s'accroupit à la même hauteur. Tu veux le cheval ? Oui, papa. Tes genoux sont dans l'herbe ? Oui, maman. Victorino arrive près du portail. Il prend son temps, les pieds dans la poussière. J'aide. Vite ! Victorino s'agenouille plus lentement. Un petit rire commence, chez Amir. Victorino baisse les yeux. Ses épaules se serrent un peu. Le rire s'arrête net. Amir ferme la bouche. Ses joues sont chaudes, un peu. On cherche le cheval ? Victorino ne répond pas tout de suite. On cherche. Tu tiens la branche, Amir ? Oui.&lt;/prosody&gt;&lt;break time="500ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Nora est au parc avec maman. Lila arrive. Elles n'ont pas la même taille. Lila est plus petite. Nora est plus grande. Les tailles sont différentes. Les &lt;emphasis&gt;corps&lt;/emphasis&gt; ont des formes différentes. Un petit rire commence. Maman parle tout de suite. Maman dit : le corps n'est pas une blague. On joue ensemble. Nora ferme la bouche. Elle tend le ballon. Elles jouent. Le ballon est doux. Plus tard, elles rentrent en classe. Sur la table, il y a de la pâte. Les tabliers tombent différemment. Encore un petit rire. Nora dit : le corps n'est pas une blague. On joue ensemble. Elles font des formes. La pâte est froide. Au parc, puis en classe, c'est pareil. On joue. On ne commente pas le corps pour rabaisser. L'amitié ne dépend pas de la forme. [pause]</t>
+          <t>Le chemin du village sent la poussière chaude. La haie de buis est serrée, un peu piquante. Une abeille va d'une fleur à l'autre. Le portail de fer est tiède sous la main. Tu as vu le portail, Amir ? Il est chaud. Le soleil l'a touché. La haie aussi. Elle pique un peu. La poussière colle aux orteils. Le buis sent le vert chaud. Une feuille tremble au bord de la haie. Sur la feuille, un &lt;emphasis&gt;éclat de buis&lt;/emphasis&gt; brille. Il brille, papa. Tu le vois, sur la feuille ? Oui, il brille. C'est petit, cet éclat. L'herbe est sèche, un peu dure. Mon cheval de bois. Il a roulé. Sous la haie ? Oui, maman. Je le veux, maintenant ! On le cherche ? Oui, papa. En ce moment, Amir cherche dans l'herbe. Les tiges piquent ses paumes. Il écarte une branche trop vite. Le bois glisse plus loin, sous les feuilles. Il est parti ! L'éclat de buis saute près du portail. Le sourire d'Amir disparaît. Dans sa poitrine, l'envie et l'inquiétude se bousculent. Ses épaules tombent un peu. Papa s'accroupit à la même hauteur. Tu veux le cheval ? Oui, papa. Tes genoux sont dans l'herbe ? Oui, maman. Victorino arrive près du portail. Il prend son temps, les pieds dans la poussière. J'aide. Vite ! Victorino s'agenouille plus lentement. Un petit rire commence, chez Amir. Victorino baisse les yeux. Ses épaules se serrent un peu. Le rire s'arrête net. Amir ferme la bouche. Ses joues sont chaudes, un peu. On cherche le cheval ? Victorino ne répond pas tout de suite. On cherche. Tu tiens la branche, Amir ? Oui. [pause]</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr"/>
@@ -1246,7 +1246,7 @@
         </is>
       </c>
       <c r="Y2" s="2" t="n">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
@@ -1254,7 +1254,7 @@
         </is>
       </c>
       <c r="AA2" s="2" t="n">
-        <v>0.96</v>
+        <v>0.98</v>
       </c>
       <c r="AB2" s="2" t="n">
         <v>1.12</v>
@@ -1280,30 +1280,30 @@
       </c>
       <c r="AH2" s="2" t="inlineStr">
         <is>
-          <t>corps</t>
+          <t>éclat de buis</t>
         </is>
       </c>
       <c r="AI2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AJ2" s="2" t="n">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="AK2" s="2" t="n">
-        <v>280</v>
+        <v>260</v>
       </c>
       <c r="AL2" s="2" t="inlineStr">
         <is>
-          <t>calm</t>
+          <t>warm</t>
         </is>
       </c>
       <c r="AM2" s="2" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>storytelling</t>
         </is>
       </c>
       <c r="AN2" s="2" t="n">
-        <v>0.333</v>
+        <v>0.36</v>
       </c>
       <c r="AO2" s="2" t="inlineStr"/>
       <c r="AP2" s="2" t="inlineStr">
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="AQ2" s="2" t="n">
-        <v>0.96</v>
+        <v>0.98</v>
       </c>
       <c r="AR2" s="2" t="n">
-        <v>0.96</v>
+        <v>0.98</v>
       </c>
       <c r="AS2" s="2" t="n">
         <v>100</v>
@@ -1326,47 +1326,73 @@
       <c r="AU2" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AV2" s="2" t="inlineStr">
+        <is>
+          <t>arc=installation; intention=émerveiller puis tendre; emotion=impatience puis gêne; intensite=2; destinataire=enfant; sous_texte=il_veut_le_cheval_maintenant; tempo=naturel puis resserré; sourire=léger puis aucun; respiration=ample puis retenue</t>
+        </is>
+      </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|La poussière du chemin sent encore le soleil.
-narrateur|La haie de buis est chaude et serrée.
+          <t>narrateur|Le chemin du village sent la poussière chaude.
+narrateur|La haie de buis est serrée, un peu piquante.
 narrateur|Une abeille va d'une fleur à l'autre.
-narrateur|Le portail de fer est tiède.
-narrateur|Un caillou blanc brille dans l'ornière.
-maman|Tu as vu le portail, Amir ?
+narrateur|Le portail de fer est tiède sous la main.
+papa|Tu as vu le portail, Amir ?
 enfant-m|Il est chaud.
-maman|Oui.
-maman|Le soleil l'a touché.
-narrateur|En ce moment, Amir cherche dans l'herbe.
-narrateur|L'herbe est sèche et un peu piquante.
+papa|Le soleil l'a touché.
+maman|La haie aussi.
+enfant-m|Elle pique un peu.
+narrateur|La poussière colle aux orteils.
+narrateur|Le buis sent le vert chaud.
+narrateur|Une feuille tremble au bord de la haie.
+narrateur|Sur la feuille, un éclat de buis brille.
+enfant-m|Il brille, papa.
+papa|Tu le vois, sur la feuille ?
+enfant-m|Oui, il brille.
+maman|C'est petit, cet éclat.
+narrateur|L'herbe est sèche, un peu dure.
 enfant-m|Mon cheval de bois.
 enfant-m|Il a roulé.
-maman|Regarde sous la haie.
+maman|Sous la haie ?
+enfant-m|Oui, maman.
+enfant-m|Je le veux, maintenant !
+papa|On le cherche ?
+enfant-m|Oui, papa.
+narrateur|En ce moment, Amir cherche dans l'herbe.
+narrateur|Les tiges piquent ses paumes.
+narrateur|Il écarte une branche trop vite.
+narrateur|Le bois glisse plus loin, sous les feuilles.
+enfant-m|Il est parti !
+narrateur|L'éclat de buis saute près du portail.
+narrateur|Le sourire d'Amir disparaît.
+narrateur|Dans sa poitrine, l'envie et l'inquiétude se bousculent.
+narrateur|Ses épaules tombent un peu.
+narrateur|Papa s'accroupit à la même hauteur.
+papa|Tu veux le cheval ?
+enfant-m|Oui, papa.
+maman|Tes genoux sont dans l'herbe ?
+enfant-m|Oui, maman.
 narrateur|Victorino arrive près du portail.
-narrateur|Ses genoux ont déjà de la poussière.
-narrateur|Victorino a un corps plus rond.
-narrateur|Amir a un corps plus mince.
-narrateur|Les corps ont des formes différentes.
-narrateur|Un petit rire commence.
-maman|Le corps n'est pas une blague.
-maman|On joue.
+narrateur|Il prend son temps, les pieds dans la poussière.
+copain|J'aide.
+enfant-m|Vite !
+narrateur|Victorino s'agenouille plus lentement.
+narrateur|Un petit rire commence, chez Amir.
+narrateur|Victorino baisse les yeux.
+narrateur|Ses épaules se serrent un peu.
+narrateur|Le rire s'arrête net.
 narrateur|Amir ferme la bouche.
+narrateur|Ses joues sont chaudes, un peu.
 enfant-m|On cherche le cheval ?
+narrateur|Victorino ne répond pas tout de suite.
 copain|On cherche.
-narrateur|Ils écartent une branche.
-narrateur|Les feuilles sentent le vert.
-narrateur|Un caillou roule.
-enfant-m|Pas lui.
-narrateur|Le bois du cheval apparaît.
-enfant-m|Te voilà.
-copain|Il a de la terre au nez.
-maman|On va le laver à la maison.</t>
+papa|Tu tiens la branche, Amir ?
+enfant-m|Oui.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>enfants_parc</t>
+          <t>abeille,chemin,haie</t>
         </is>
       </c>
     </row>
@@ -1398,12 +1424,12 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Le corps n'est pas une blague. Que fait-on ?</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Le corps n'est pas une &lt;emphasis level="moderate"&gt;blague&lt;/emphasis&gt;. Que fait-on ?&lt;/prosody&gt;&lt;break time="700ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Le &lt;emphasis&gt;corps&lt;/emphasis&gt; n'est pas une blague. Que fait-on ?</t>
+          <t>&lt;soft&gt;&lt;slow&gt;Le corps n'est pas une &lt;emphasis&gt;blague&lt;/emphasis&gt;. Que fait-on ?&lt;/slow&gt;&lt;/soft&gt; [pause]</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -1428,7 +1454,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>On joue. Le corps n'est pas une blague. Que fait-on ?</t>
+          <t>On joue. Que fait Amir ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1466,18 +1492,18 @@
         </is>
       </c>
       <c r="Y3" s="2" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>slow</t>
         </is>
       </c>
       <c r="AA3" s="2" t="n">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1492,38 +1518,38 @@
       <c r="AE3" s="2" t="inlineStr"/>
       <c r="AF3" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>soft</t>
         </is>
       </c>
       <c r="AG3" s="2" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AH3" s="2" t="inlineStr">
         <is>
-          <t>corps</t>
+          <t>blague</t>
         </is>
       </c>
       <c r="AI3" s="2" t="n">
         <v>200</v>
       </c>
       <c r="AJ3" s="2" t="n">
-        <v>250</v>
+        <v>700</v>
       </c>
       <c r="AK3" s="2" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
       <c r="AL3" s="2" t="inlineStr">
         <is>
-          <t>warm</t>
+          <t>focused</t>
         </is>
       </c>
       <c r="AM3" s="2" t="inlineStr">
         <is>
-          <t>rise</t>
+          <t>rising</t>
         </is>
       </c>
       <c r="AN3" s="2" t="n">
-        <v>0.333</v>
+        <v>0.32</v>
       </c>
       <c r="AO3" s="2" t="inlineStr"/>
       <c r="AP3" s="2" t="inlineStr">
@@ -1532,23 +1558,23 @@
         </is>
       </c>
       <c r="AQ3" s="2" t="n">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="AR3" s="2" t="n">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="AS3" s="2" t="n">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="AT3" s="2" t="n">
         <v>50</v>
       </c>
       <c r="AU3" s="2" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AV3" s="2" t="inlineStr">
         <is>
-          <t>question d'écoute, ne change pas le cours</t>
+          <t>arc=indice; intention=faire_deviner; emotion=attention; intensite=1; destinataire=enfant; sous_texte=le_rire_s_est_arrete_ils_cherchent_ensemble; tempo=suspendu; sourire=aucun; respiration=courte_avant_question</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
@@ -1581,17 +1607,17 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Sur la véranda, l'argile attend. Elle est froide et un peu grise. Amir lave le cheval. L'eau fait un filet brun. Le bois redevient lisse. Il est propre. Il a besoin d'une écurie. On la fait. Ils pressent l'argile. Ça fait un bruit mou. Amir dresse un mur. Victorino dresse l'autre mur. Un mur s'affaisse. Il est fatigué. On le tient ensemble. Victorino appuie tout doux. Amir pose un toit plat. Le cheval entre dans l'écurie. Sa jambe de bois touche l'argile. Il est à la maison. Bravo, Amir. Tu as trouvé le cheval. Vous jouez. L'amitié ne dépend pas de la forme.</t>
+          <t>Amir tend une branche vers Victorino. Victorino la prend, sans se presser. Tu tiens ? Oui. Ils écartent les feuilles, ensemble. Les feuilles sentent le vert. Un caillou roule. Pas lui. Plus bas. Le bois du cheval apparaît. Te voilà. Il a de la terre au nez. On le lave, sur la véranda ? Oui, maman. Je pousse le portail. La véranda est à l'ombre, un peu froide. Un bac d'eau attend près du banc. Amir lave le cheval. L'eau fait un filet brun. Il est propre. Il a besoin d'une écurie ? Oui, maintenant ! On la fait. L'argile attend sur une planche. Elle est froide, un peu grise. Amir dresse un mur trop vite. Le mur s'affaisse, mou. Oh. Le sourire ne revient pas. Amir refuse de foncer. Il pose les paumes à plat. Personne ne dit la suite. Il écoute l'abeille, près de la haie. Attends. Victorino appuie de l'autre côté. Les deux murs tiennent, un peu. Un toit ? Pas trop vite. Amir pose un toit plat. Le cheval entre dans l'écurie. Sa jambe de bois touche l'argile. Il est à la maison. Merci, Amir. Papa a vu les deux mains sur l'argile. Victorino, tu as vu le cheval ? Oui. Il tient. Le ventre d'Amir se desserre.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Sur la véranda, l'argile attend. Elle est froide et un peu grise. Amir lave le cheval. L'eau fait un filet brun. Le bois redevient lisse. Il est propre. Il a besoin d'une écurie. On la fait. Ils pressent l'argile. Ça fait un bruit mou. Amir dresse un mur. Victorino dresse l'autre mur. Un mur s'affaisse. Il est fatigué. On le tient ensemble. Victorino appuie tout doux. Amir pose un toit plat. Le cheval entre dans l'écurie. Sa jambe de bois touche l'argile. Il est à la maison. Bravo, Amir. Tu as trouvé le cheval. Vous jouez. L'amitié ne dépend pas de la forme.</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Amir tend une branche vers Victorino. Victorino la prend, sans se presser. Tu tiens ? Oui. Ils écartent les feuilles, ensemble. Les feuilles sentent le vert. Un caillou roule. Pas lui. Plus bas. Le bois du cheval apparaît. Te voilà. Il a de la terre au nez. On le lave, sur la véranda ? Oui, maman. Je pousse le portail. La véranda est à l'ombre, un peu froide. Un bac d'eau attend près du banc. Amir lave le cheval. L'eau fait un filet brun. Il est propre. Il a besoin d'une &lt;emphasis level="moderate"&gt;écurie&lt;/emphasis&gt; ? Oui, maintenant ! On la fait. L'argile attend sur une planche. Elle est froide, un peu grise. Amir dresse un mur trop vite. Le mur s'affaisse, mou. Oh. Le sourire ne revient pas. Amir refuse de foncer. Il pose les paumes à plat. Personne ne dit la suite. Il écoute l'abeille, près de la haie. Attends. Victorino appuie de l'autre côté. Les deux murs tiennent, un peu. Un toit ? Pas trop vite. Amir pose un toit plat. Le cheval entre dans l'écurie. Sa jambe de bois touche l'argile. Il est à la maison. Merci, Amir. Papa a vu les deux mains sur l'argile. Victorino, tu as vu le cheval ? Oui. Il tient. Le ventre d'Amir se desserre.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Nora a entendu maman. Le &lt;emphasis&gt;corps&lt;/emphasis&gt; n'est pas une blague. Nora et Lila ont joué. Deux fois. [pause]</t>
+          <t>Amir tend une branche vers Victorino. Victorino la prend, sans se presser. Tu tiens ? Oui. Ils écartent les feuilles, ensemble. Les feuilles sentent le vert. Un caillou roule. Pas lui. Plus bas. Le bois du cheval apparaît. Te voilà. Il a de la terre au nez. On le lave, sur la véranda ? Oui, maman. Je pousse le portail. La véranda est à l'ombre, un peu froide. Un bac d'eau attend près du banc. Amir lave le cheval. L'eau fait un filet brun. Il est propre. Il a besoin d'une &lt;emphasis&gt;écurie&lt;/emphasis&gt; ? Oui, maintenant ! On la fait. L'argile attend sur une planche. Elle est froide, un peu grise. Amir dresse un mur trop vite. Le mur s'affaisse, mou. Oh. Le sourire ne revient pas. Amir refuse de foncer. Il pose les paumes à plat. Personne ne dit la suite. Il écoute l'abeille, près de la haie. Attends. Victorino appuie de l'autre côté. Les deux murs tiennent, un peu. Un toit ? Pas trop vite. Amir pose un toit plat. Le cheval entre dans l'écurie. Sa jambe de bois touche l'argile. Il est à la maison. Merci, Amir. Papa a vu les deux mains sur l'argile. Victorino, tu as vu le cheval ? Oui. Il tient. Le ventre d'Amir se desserre. [pause]</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr"/>
@@ -1638,7 +1664,7 @@
         </is>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
@@ -1646,10 +1672,10 @@
         </is>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1672,30 +1698,30 @@
       </c>
       <c r="AH4" s="2" t="inlineStr">
         <is>
-          <t>corps</t>
+          <t>écurie</t>
         </is>
       </c>
       <c r="AI4" s="2" t="n">
         <v>200</v>
       </c>
       <c r="AJ4" s="2" t="n">
-        <v>450</v>
+        <v>560</v>
       </c>
       <c r="AK4" s="2" t="n">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="AL4" s="2" t="inlineStr">
         <is>
-          <t>calm</t>
+          <t>bright</t>
         </is>
       </c>
       <c r="AM4" s="2" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>falling</t>
         </is>
       </c>
       <c r="AN4" s="2" t="n">
-        <v>0.333</v>
+        <v>0.35</v>
       </c>
       <c r="AO4" s="2" t="inlineStr"/>
       <c r="AP4" s="2" t="inlineStr">
@@ -1704,10 +1730,10 @@
         </is>
       </c>
       <c r="AQ4" s="2" t="n">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="AR4" s="2" t="n">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="AS4" s="2" t="n">
         <v>100</v>
@@ -1720,35 +1746,64 @@
       </c>
       <c r="AV4" s="2" t="inlineStr">
         <is>
-          <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
+          <t>arc=résolution; intention=faire_vivre_le_geste; emotion=retenue puis fierté_calme; intensite=2; destinataire=enfant; sous_texte=ils_tiennent_la_branche_puis_l_argile; tempo=naturel; sourire=léger; respiration=relâchée</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Sur la véranda, l'argile attend.
-narrateur|Elle est froide et un peu grise.
+          <t>narrateur|Amir tend une branche vers Victorino.
+narrateur|Victorino la prend, sans se presser.
+enfant-m|Tu tiens ?
+copain|Oui.
+narrateur|Ils écartent les feuilles, ensemble.
+narrateur|Les feuilles sentent le vert.
+narrateur|Un caillou roule.
+enfant-m|Pas lui.
+copain|Plus bas.
+narrateur|Le bois du cheval apparaît.
+enfant-m|Te voilà.
+copain|Il a de la terre au nez.
+maman|On le lave, sur la véranda ?
+enfant-m|Oui, maman.
+papa|Je pousse le portail.
+narrateur|La véranda est à l'ombre, un peu froide.
+narrateur|Un bac d'eau attend près du banc.
 narrateur|Amir lave le cheval.
 narrateur|L'eau fait un filet brun.
-narrateur|Le bois redevient lisse.
 enfant-m|Il est propre.
-maman|Il a besoin d'une écurie.
+papa|Il a besoin d'une écurie ?
+enfant-m|Oui, maintenant !
 copain|On la fait.
-narrateur|Ils pressent l'argile.
-narrateur|Ça fait un bruit mou.
-narrateur|Amir dresse un mur.
-narrateur|Victorino dresse l'autre mur.
-narrateur|Un mur s'affaisse.
-enfant-m|Il est fatigué.
-maman|On le tient ensemble.
-narrateur|Victorino appuie tout doux.
+narrateur|L'argile attend sur une planche.
+narrateur|Elle est froide, un peu grise.
+narrateur|Amir dresse un mur trop vite.
+narrateur|Le mur s'affaisse, mou.
+enfant-m|Oh.
+narrateur|Le sourire ne revient pas.
+narrateur|Amir refuse de foncer.
+narrateur|Il pose les paumes à plat.
+narrateur|Personne ne dit la suite.
+narrateur|Il écoute l'abeille, près de la haie.
+copain|Attends.
+narrateur|Victorino appuie de l'autre côté.
+narrateur|Les deux murs tiennent, un peu.
+enfant-m|Un toit ?
+copain|Pas trop vite.
 narrateur|Amir pose un toit plat.
 narrateur|Le cheval entre dans l'écurie.
 narrateur|Sa jambe de bois touche l'argile.
 copain|Il est à la maison.
-maman|Bravo, Amir.
-maman|Tu as trouvé le cheval.
-maman|Vous jouez.
-maman|L'amitié ne dépend pas de la forme.</t>
+papa|Merci, Amir.
+narrateur|Papa a vu les deux mains sur l'argile.
+maman|Victorino, tu as vu le cheval ?
+copain|Oui.
+enfant-m|Il tient.
+narrateur|Le ventre d'Amir se desserre.</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>eau,argile</t>
         </is>
       </c>
     </row>
@@ -1775,17 +1830,17 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>On laisse sécher ? Oui. L'argile devient un peu plus claire. Le cheval de bois attend dessous. Il dort. Tout petit. Tu as fini de presser l'argile ? Oui, maman. Ils se lavent les mains. L'eau est tiède. Dehors, le portail est encore chaud. Une abeille passe encore près de la haie. On le touchera demain. Merci, Victorino. Merci, Amir.</t>
+          <t>Amir veut le toit plus haut, d'un coup. Il pousse l'argile trop vite. Le toit glisse vers le bord. Ça tombe ! La jambe de bois s'enfonce un peu. Attends. Amir veut rattraper le toit, d'un coup. Amir refuse de foncer. Ses épaules se serrent un peu. Ça tape, dans sa poitrine. Personne ne dit la suite. Il regarde la haie, par la véranda. L'éclat, papa ? Tu le vois, toi ? Sur la feuille. L'éclat de buis revient, sur la feuille. Le cheval, Amir ? Oui. Victorino tient le mur, sans parler. Amir pose le toit, plus lentement. La jambe de bois repose, droite. Il tient. Il dort. Tes mains sont propres ? Un peu d'argile, papa. L'eau est tiède. Ils se lavent les mains, près du bac. Dehors, le portail reste tiède. L'abeille est là. Près de la haie ? Oui, papa.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>On laisse sécher ? Oui. L'argile devient un peu plus claire. Le cheval de bois attend dessous. Il dort. Tout petit. Tu as fini de presser l'argile ? Oui, maman. Ils se lavent les mains. L'eau est tiède. Dehors, le portail est encore chaud. Une abeille passe encore près de la haie. On le touchera demain. Merci, Victorino. Merci, Amir.</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Amir veut le toit plus haut, d'un coup. Il pousse l'argile trop vite. Le toit glisse vers le bord. Ça tombe ! La jambe de bois s'enfonce un peu. Attends. Amir veut rattraper le toit, d'un coup. Amir refuse de foncer. Ses épaules se serrent un peu. Ça tape, dans sa poitrine. Personne ne dit la suite. Il regarde la haie, par la véranda. L'éclat, papa ? Tu le vois, toi ? Sur la feuille. L'&lt;emphasis level="moderate"&gt;éclat de buis&lt;/emphasis&gt; revient, sur la feuille. Le cheval, Amir ? Oui. Victorino tient le mur, sans parler. Amir pose le toit, plus lentement. La jambe de bois repose, droite. Il tient. Il dort. Tes mains sont propres ? Un peu d'argile, papa. L'eau est tiède. Ils se lavent les mains, près du bac. Dehors, le portail reste tiède. L'abeille est là. Près de la haie ? Oui, papa.&lt;/prosody&gt;&lt;break time="420ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Nora range un morceau de pâte. Lila range un emporte-pièce. Merci, dit maman. [pause]</t>
+          <t>Amir veut le toit plus haut, d'un coup. Il pousse l'argile trop vite. Le toit glisse vers le bord. Ça tombe ! La jambe de bois s'enfonce un peu. Attends. Amir veut rattraper le toit, d'un coup. Amir refuse de foncer. Ses épaules se serrent un peu. Ça tape, dans sa poitrine. Personne ne dit la suite. Il regarde la haie, par la véranda. L'éclat, papa ? Tu le vois, toi ? Sur la feuille. L'&lt;emphasis&gt;éclat de buis&lt;/emphasis&gt; revient, sur la feuille. Le cheval, Amir ? Oui. Victorino tient le mur, sans parler. Amir pose le toit, plus lentement. La jambe de bois repose, droite. Il tient. Il dort. Tes mains sont propres ? Un peu d'argile, papa. L'eau est tiède. Ils se lavent les mains, près du bac. Dehors, le portail reste tiède. L'abeille est là. Près de la haie ? Oui, papa. [pause]</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr"/>
@@ -1832,7 +1887,7 @@
         </is>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
@@ -1840,10 +1895,10 @@
         </is>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>0.96</v>
+        <v>1</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1864,28 +1919,32 @@
       <c r="AG5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AH5" s="2" t="inlineStr"/>
+      <c r="AH5" s="2" t="inlineStr">
+        <is>
+          <t>éclat de buis</t>
+        </is>
+      </c>
       <c r="AI5" s="2" t="n">
         <v>200</v>
       </c>
       <c r="AJ5" s="2" t="n">
-        <v>450</v>
+        <v>420</v>
       </c>
       <c r="AK5" s="2" t="n">
-        <v>280</v>
+        <v>250</v>
       </c>
       <c r="AL5" s="2" t="inlineStr">
         <is>
-          <t>calm</t>
+          <t>lively</t>
         </is>
       </c>
       <c r="AM5" s="2" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>dynamic</t>
         </is>
       </c>
       <c r="AN5" s="2" t="n">
-        <v>0.333</v>
+        <v>0.37</v>
       </c>
       <c r="AO5" s="2" t="inlineStr"/>
       <c r="AP5" s="2" t="inlineStr">
@@ -1894,10 +1953,10 @@
         </is>
       </c>
       <c r="AQ5" s="2" t="n">
-        <v>0.96</v>
+        <v>1</v>
       </c>
       <c r="AR5" s="2" t="n">
-        <v>0.96</v>
+        <v>1</v>
       </c>
       <c r="AS5" s="2" t="n">
         <v>100</v>
@@ -1908,24 +1967,49 @@
       <c r="AU5" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AV5" s="2" t="inlineStr">
+        <is>
+          <t>arc=action; intention=entraîner; emotion=élan puis prudence; intensite=2; destinataire=enfant; sous_texte=il_refuse_de_rattraper_le_toit_trop_vite; tempo=vif puis posé; sourire=léger; respiration=courte</t>
+        </is>
+      </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>maman|On laisse sécher ?
+          <t>narrateur|Amir veut le toit plus haut, d'un coup.
+narrateur|Il pousse l'argile trop vite.
+narrateur|Le toit glisse vers le bord.
+enfant-m|Ça tombe !
+narrateur|La jambe de bois s'enfonce un peu.
+copain|Attends.
+narrateur|Amir veut rattraper le toit, d'un coup.
+narrateur|Amir refuse de foncer.
+narrateur|Ses épaules se serrent un peu.
+narrateur|Ça tape, dans sa poitrine.
+narrateur|Personne ne dit la suite.
+narrateur|Il regarde la haie, par la véranda.
+enfant-m|L'éclat, papa ?
+papa|Tu le vois, toi ?
+enfant-m|Sur la feuille.
+narrateur|L'éclat de buis revient, sur la feuille.
+maman|Le cheval, Amir ?
 enfant-m|Oui.
-narrateur|L'argile devient un peu plus claire.
-narrateur|Le cheval de bois attend dessous.
-copain|Il dort.
-enfant-m|Tout petit.
-maman|Tu as fini de presser l'argile ?
-enfant-m|Oui, maman.
-narrateur|Ils se lavent les mains.
-narrateur|L'eau est tiède.
-narrateur|Dehors, le portail est encore chaud.
-narrateur|Une abeille passe encore près de la haie.
-maman|On le touchera demain.
-enfant-m|Merci, Victorino.
-copain|Merci, Amir.</t>
+narrateur|Victorino tient le mur, sans parler.
+narrateur|Amir pose le toit, plus lentement.
+narrateur|La jambe de bois repose, droite.
+copain|Il tient.
+enfant-m|Il dort.
+papa|Tes mains sont propres ?
+enfant-m|Un peu d'argile, papa.
+maman|L'eau est tiède.
+narrateur|Ils se lavent les mains, près du bac.
+narrateur|Dehors, le portail reste tiède.
+enfant-m|L'abeille est là.
+papa|Près de la haie ?
+enfant-m|Oui, papa.</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>argile</t>
         </is>
       </c>
     </row>
@@ -1952,17 +2036,17 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>On a trouvé le cheval. On a fait l'écurie. Vous avez joué. La haie garde un peu de poussière.</t>
+          <t>Ils restent près de la planche. Le cheval de bois attend sous le toit. L'éclat est là, papa. Tu le vois sur la feuille ? Oui, papa. On est bien, ici. Dehors, le chemin sent la poussière. Une abeille passe près de la haie. Il est à la maison. Il est à la maison, Amir. Oui, maman. Amir pose la joue près du bois. Le bois est froid, un peu. C'est froid. Tu le sens sur tes joues ? Oui, il est froid. Le nez a de la terre. Le nez du cheval porte une trace. La haie garde un peu de poussière. L'éclat de buis tient sur la feuille.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>On a trouvé le cheval. On a fait l'écurie. Vous avez joué. La haie garde un peu de poussière.</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Ils restent près de la planche. Le cheval de bois attend sous le toit. L'éclat est là, papa. Tu le vois sur la feuille ? Oui, papa. On est bien, ici. Dehors, le chemin sent la poussière. Une abeille passe près de la haie. Il est à la maison. Il est à la maison, Amir. Oui, maman. Amir pose la joue près du bois. Le bois est froid, un peu. C'est froid. Tu le sens sur tes joues ? Oui, il est froid. Le nez a de la terre. Le nez du cheval porte une trace. La haie garde un peu de poussière. L'&lt;emphasis level="moderate"&gt;éclat de buis&lt;/emphasis&gt; tient sur la feuille.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>&lt;lower-pitch&gt;&lt;soft&gt;L'histoire est finie.&lt;/soft&gt;&lt;/lower-pitch&gt; [pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Ils restent près de la planche. Le cheval de bois attend sous le toit. L'éclat est là, papa. Tu le vois sur la feuille ? Oui, papa. On est bien, ici. Dehors, le chemin sent la poussière. Une abeille passe près de la haie. Il est à la maison. Il est à la maison, Amir. Oui, maman. Amir pose la joue près du bois. Le bois est froid, un peu. C'est froid. Tu le sens sur tes joues ? Oui, il est froid. Le nez a de la terre. Le nez du cheval porte une trace. La haie garde un peu de poussière. L'&lt;emphasis&gt;éclat de buis&lt;/emphasis&gt; tient sur la feuille.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr"/>
@@ -2009,7 +2093,7 @@
         </is>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>136</v>
+        <v>118</v>
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
@@ -2017,10 +2101,10 @@
         </is>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.12</v>
+        <v>1.28</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2029,12 +2113,12 @@
       </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>-2st</t>
         </is>
       </c>
       <c r="AE6" s="2" t="inlineStr">
         <is>
-          <t>lower-pitch</t>
+          <t>low-pitch</t>
         </is>
       </c>
       <c r="AF6" s="2" t="inlineStr">
@@ -2043,17 +2127,21 @@
         </is>
       </c>
       <c r="AG6" s="2" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AH6" s="2" t="inlineStr"/>
+        <v>-3</v>
+      </c>
+      <c r="AH6" s="2" t="inlineStr">
+        <is>
+          <t>éclat de buis</t>
+        </is>
+      </c>
       <c r="AI6" s="2" t="n">
         <v>200</v>
       </c>
       <c r="AJ6" s="2" t="n">
-        <v>600</v>
+        <v>900</v>
       </c>
       <c r="AK6" s="2" t="n">
-        <v>280</v>
+        <v>340</v>
       </c>
       <c r="AL6" s="2" t="inlineStr">
         <is>
@@ -2062,11 +2150,11 @@
       </c>
       <c r="AM6" s="2" t="inlineStr">
         <is>
-          <t>fall</t>
+          <t>falling</t>
         </is>
       </c>
       <c r="AN6" s="2" t="n">
-        <v>0.333</v>
+        <v>0.31</v>
       </c>
       <c r="AO6" s="2" t="inlineStr"/>
       <c r="AP6" s="2" t="inlineStr">
@@ -2075,27 +2163,47 @@
         </is>
       </c>
       <c r="AQ6" s="2" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR6" s="2" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AS6" s="2" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AT6" s="2" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="AU6" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV6" s="2" t="inlineStr"/>
+        <v>12</v>
+      </c>
+      <c r="AV6" s="2" t="inlineStr">
+        <is>
+          <t>arc=retour; intention=refermer; emotion=tendresse et fierté_calme; intensite=1; destinataire=enfant; sous_texte=l_eclat_du_debut_tient_sur_la_feuille; tempo=posé; sourire=léger; respiration=ample</t>
+        </is>
+      </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>enfant-m|On a trouvé le cheval.
-copain|On a fait l'écurie.
-maman|Vous avez joué.
-narrateur|La haie garde un peu de poussière.</t>
+          <t>narrateur|Ils restent près de la planche.
+narrateur|Le cheval de bois attend sous le toit.
+enfant-m|L'éclat est là, papa.
+papa|Tu le vois sur la feuille ?
+enfant-m|Oui, papa.
+maman|On est bien, ici.
+narrateur|Dehors, le chemin sent la poussière.
+narrateur|Une abeille passe près de la haie.
+enfant-m|Il est à la maison.
+maman|Il est à la maison, Amir.
+enfant-m|Oui, maman.
+narrateur|Amir pose la joue près du bois.
+narrateur|Le bois est froid, un peu.
+enfant-m|C'est froid.
+papa|Tu le sens sur tes joues ?
+enfant-m|Oui, il est froid.
+copain|Le nez a de la terre.
+narrateur|Le nez du cheval porte une trace.
+narrateur|La haie garde un peu de poussière.
+narrateur|L'éclat de buis tient sur la feuille.</t>
         </is>
       </c>
     </row>
@@ -2116,7 +2224,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A12"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2201,6 +2309,13 @@
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
